--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619078.9295637934</v>
+        <v>619079</v>
       </c>
       <c r="R2" t="n">
-        <v>6689287.769226862</v>
+        <v>6689288</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1996-07-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1996-07-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619078.9295637934</v>
+        <v>619079</v>
       </c>
       <c r="R3" t="n">
-        <v>6689287.769226862</v>
+        <v>6689288</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -874,19 +854,9 @@
           <t>1996-07-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1996-07-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619078.9295637934</v>
+        <v>619079</v>
       </c>
       <c r="R4" t="n">
-        <v>6689287.769226862</v>
+        <v>6689288</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1000,19 +965,9 @@
           <t>1996-07-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1996-07-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,12 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619078.9295637934</v>
+        <v>619079</v>
       </c>
       <c r="R5" t="n">
-        <v>6689287.769226862</v>
+        <v>6689288</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1126,19 +1076,9 @@
           <t>1996-07-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1996-07-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,12 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100668</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619078.9295637934</v>
+        <v>619079</v>
       </c>
       <c r="R6" t="n">
-        <v>6689287.769226862</v>
+        <v>6689288</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1252,19 +1187,9 @@
           <t>1996-07-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1996-07-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>101665</v>
+        <v>101673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>103086</v>
+        <v>103094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>101673</v>
+        <v>101678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>103094</v>
+        <v>103106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>103168</v>
+        <v>103173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45278-2022 artfynd.xlsx
+++ b/artfynd/A 45278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99162335</v>
       </c>
       <c r="B2" t="n">
-        <v>101744</v>
+        <v>101752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>99162328</v>
       </c>
       <c r="B3" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>99162316</v>
       </c>
       <c r="B4" t="n">
-        <v>103173</v>
+        <v>103181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>99162329</v>
       </c>
       <c r="B5" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>99162287</v>
       </c>
       <c r="B6" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
